--- a/output/CodeSystem-PdexMemberAttributionCS.xlsx
+++ b/output/CodeSystem-PdexMemberAttributionCS.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="51">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.1.1</t>
+    <t>2.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-17T14:48:28-05:00</t>
+    <t>2026-03-17T22:49:33-04:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -132,21 +132,24 @@
     <t>Count</t>
   </si>
   <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>Level</t>
+  </si>
+  <si>
+    <t>Code</t>
+  </si>
+  <si>
+    <t>Display</t>
+  </si>
+  <si>
+    <t>Definition</t>
+  </si>
+  <si>
     <t>1</t>
   </si>
   <si>
-    <t>Level</t>
-  </si>
-  <si>
-    <t>Code</t>
-  </si>
-  <si>
-    <t>Display</t>
-  </si>
-  <si>
-    <t>Definition</t>
-  </si>
-  <si>
     <t>pdexprovidergroup</t>
   </si>
   <si>
@@ -154,6 +157,15 @@
   </si>
   <si>
     <t>Group of members used for PDex Provider Access API. Group is generated by an Attribution process.</t>
+  </si>
+  <si>
+    <t>pdex-member</t>
+  </si>
+  <si>
+    <t>PDex Member</t>
+  </si>
+  <si>
+    <t>Identifies a characteristic that references a member/patient in a PDex group.</t>
   </si>
 </sst>
 </file>
@@ -481,7 +493,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D3"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -500,16 +512,30 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="B2" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="C2" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="D2" t="s" s="2">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="2">
         <v>44</v>
       </c>
-      <c r="C2" t="s" s="2">
-        <v>45</v>
-      </c>
-      <c r="D2" t="s" s="2">
-        <v>46</v>
+      <c r="B3" t="s" s="2">
+        <v>48</v>
+      </c>
+      <c r="C3" t="s" s="2">
+        <v>49</v>
+      </c>
+      <c r="D3" t="s" s="2">
+        <v>50</v>
       </c>
     </row>
   </sheetData>

--- a/output/CodeSystem-PdexMemberAttributionCS.xlsx
+++ b/output/CodeSystem-PdexMemberAttributionCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-17T22:49:33-04:00</t>
+    <t>2026-03-19T09:51:30-04:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/output/CodeSystem-PdexMemberAttributionCS.xlsx
+++ b/output/CodeSystem-PdexMemberAttributionCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-19T09:51:30-04:00</t>
+    <t>2026-03-31T21:00:10-04:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/output/CodeSystem-PdexMemberAttributionCS.xlsx
+++ b/output/CodeSystem-PdexMemberAttributionCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-31T21:00:10-04:00</t>
+    <t>2026-05-29T12:37:47-04:00</t>
   </si>
   <si>
     <t>Publisher</t>
